--- a/Analysis/exports/backtest_results.xlsx
+++ b/Analysis/exports/backtest_results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Pick Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pick Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,52 +418,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Screener</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Pick ₹</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>D+1 %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>D+1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>D+3 %</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>D+3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>D+5 %</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>D+5</t>
         </is>
@@ -2896,42 +2884,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Picks</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Hit Rate 1D</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Avg Return 1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Hit Rate 3D</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Avg Return 3D</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Hit Rate 5D</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Avg Return 5D</t>
         </is>

--- a/Analysis/exports/backtest_results.xlsx
+++ b/Analysis/exports/backtest_results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pick Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pick Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,16 +26,36 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001D4ED8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +63,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,2454 +462,2826 @@
   </sheetPr>
   <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Screener</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Pick ₹</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>D+1 %</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>D+1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>D+3 %</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>D+3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>D+5 %</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>D+5</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>SAIL</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>200.0</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="E2" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>LODHA</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>1274.0</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="E3" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>PAYTM</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>1650.9</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="E4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>5169.2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="E5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>KALYANKJIL</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>615.8</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="E6" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>NYKAA</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>338.0</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="E7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>SOLARINDS</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>20400.0</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="E8" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>ATHERENERG</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>1616.3</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="E9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>NMDC</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>86.76</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="E10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>JSWSTEEL</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>1337.5</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
+      <c r="E11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>TECHM</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>1640.9</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
+      <c r="E12" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>OFSS</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>12190.0</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
+      <c r="E13" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>SIEMENS</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>4089.0</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
+      <c r="E14" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>COFORGE</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>2014.6</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
+      <c r="E15" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>ZYDUSLIFE</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>1189.2</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
+      <c r="E16" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>LAURUSLABS</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>1938.5</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
+      <c r="E17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>GLENMARK</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>2515.0</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
+      <c r="E18" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>3168.5</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
+      <c r="E19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>LICHSGFIN</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>535.0</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
+      <c r="E20" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>SAGILITY</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>46.34</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
+      <c r="E21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>BAJFINANCE</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>1079.9</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
+      <c r="E22" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>ASIANPAINT</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>2608.7</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
+      <c r="E23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>CAMS</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>762.0</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
+      <c r="E24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>BHARTIARTL</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>1882.4</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
+      <c r="E25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>ULTRACEMCO</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>11589.0</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
+      <c r="E26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>HCLTECH</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>1316.1</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
+      <c r="E27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>MANKIND</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>2382.9</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
+      <c r="E28" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>HAL</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>4861.1</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
+      <c r="E29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>INDUSINDBK</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>994.0</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
+      <c r="E30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>NAM-INDIA</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>1204.0</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
+      <c r="E31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>TATAELXSI</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>3685.0</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
+      <c r="E32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>NESTLEIND</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>1454.6</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
+      <c r="E33" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>INDIGO</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>5166.0</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
+      <c r="E34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>MARICO</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>833.5</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
+      <c r="E35" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>GAIL</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>171.1</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
+      <c r="E36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>SBIN</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>1047.5</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
+      <c r="E37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>TRENT</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>2898.0</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
+      <c r="E38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>IEX</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>121.8</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
+      <c r="E39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>GODFRYPHLP</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>2123.7</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
+      <c r="E40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>BHARATFORG</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>2050.0</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
+      <c r="E41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>EICHERMOT</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>8059.0</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
+      <c r="E42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>ASHOKLEY</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>175.77</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
+      <c r="E43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>JUBLFOOD</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>504.0</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
+      <c r="E44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>DLF</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>679.8</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
+      <c r="E45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>RADICO</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>4606.0</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
+      <c r="E46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>LTF</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>314.3</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
+      <c r="E47" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>ABB</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>7490.0</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
+      <c r="E48" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>AUROPHARMA</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>1637.0</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
+      <c r="E49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>INDIANB</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>882.4</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
+      <c r="E50" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>CHOLAFIN</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>1862.9</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
+      <c r="E51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>PNB</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>115.4</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
+      <c r="E52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>RBLBANK</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>382.0</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
+      <c r="E53" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>11910.0</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
+      <c r="E54" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>PIDILITIND</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>1656.0</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
+      <c r="E55" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UNITDSPR</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>1510.0</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
+      <c r="E56" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>TECHM</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>1640.9</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
+      <c r="E57" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>4045.8</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
+      <c r="E58" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>SUPREMEIND</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>3636.9</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
+      <c r="E59" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>2002.0</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
+      <c r="E60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>5169.2</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
+      <c r="E61" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2882,204 +3300,214 @@
   </sheetPr>
   <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Picks</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Hit Rate 1D</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Avg Return 1D</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Hit Rate 3D</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Avg Return 3D</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Hit Rate 5D</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avg Return 5D</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>All Picks</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Probable Upside</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Support Entry</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Consolidation Breakout</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/Analysis/exports/backtest_results.xlsx
+++ b/Analysis/exports/backtest_results.xlsx
@@ -32,7 +32,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +52,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -93,6 +98,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -460,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -549,11 +557,11 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v/>
+        <v>-2.5</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
@@ -595,11 +603,11 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v/>
+        <v>-5.92</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
@@ -640,12 +648,12 @@
           <t>1650.9</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
-        <v/>
+      <c r="E4" s="5" t="n">
+        <v>4.01</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
@@ -687,11 +695,11 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v/>
+        <v>-1.29</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
@@ -733,11 +741,11 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v/>
+        <v>-2.4</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
@@ -778,12 +786,12 @@
           <t>338.0</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
-        <v/>
+      <c r="E7" s="5" t="n">
+        <v>4.14</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
@@ -825,11 +833,11 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v/>
+        <v>-1.43</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
@@ -870,12 +878,12 @@
           <t>1616.3</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
-        <v/>
+      <c r="E9" s="5" t="n">
+        <v>6.27</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
@@ -916,12 +924,12 @@
           <t>86.76</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n">
-        <v/>
+      <c r="E10" s="5" t="n">
+        <v>1.66</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
@@ -963,11 +971,11 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v/>
+        <v>-2.04</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
@@ -1009,11 +1017,11 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v/>
+        <v>-0.79</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
@@ -1054,12 +1062,12 @@
           <t>12190.0</t>
         </is>
       </c>
-      <c r="E13" s="3" t="n">
-        <v/>
+      <c r="E13" s="5" t="n">
+        <v>2.87</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
@@ -1101,11 +1109,11 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v/>
+        <v>-1.44</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
@@ -1147,11 +1155,11 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v/>
+        <v>-1.45</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
@@ -1193,11 +1201,11 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v/>
+        <v>-2.49</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
@@ -1239,11 +1247,11 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v/>
+        <v>-1.21</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
@@ -1285,11 +1293,11 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v/>
+        <v>-1.29</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
@@ -1331,11 +1339,11 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v/>
+        <v>-9.76</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
@@ -1376,12 +1384,12 @@
           <t>535.0</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n">
-        <v/>
+      <c r="E20" s="5" t="n">
+        <v>0.64</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
@@ -1422,12 +1430,12 @@
           <t>46.34</t>
         </is>
       </c>
-      <c r="E21" s="3" t="n">
-        <v/>
+      <c r="E21" s="5" t="n">
+        <v>1.53</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
@@ -1469,11 +1477,11 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v/>
+        <v>-2.12</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
@@ -1514,12 +1522,12 @@
           <t>2608.7</t>
         </is>
       </c>
-      <c r="E23" s="3" t="n">
-        <v/>
+      <c r="E23" s="5" t="n">
+        <v>1.72</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
@@ -1560,12 +1568,12 @@
           <t>762.0</t>
         </is>
       </c>
-      <c r="E24" s="3" t="n">
-        <v/>
+      <c r="E24" s="5" t="n">
+        <v>2.62</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
@@ -1607,11 +1615,11 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v/>
+        <v>-3.75</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
@@ -1653,11 +1661,11 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v/>
+        <v>-1.2</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
@@ -1699,11 +1707,11 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v/>
+        <v>-0.3</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
@@ -1744,12 +1752,12 @@
           <t>2382.9</t>
         </is>
       </c>
-      <c r="E28" s="3" t="n">
-        <v/>
+      <c r="E28" s="5" t="n">
+        <v>1.52</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
@@ -1791,11 +1799,11 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v/>
+        <v>-1.22</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
@@ -1836,12 +1844,12 @@
           <t>994.0</t>
         </is>
       </c>
-      <c r="E30" s="3" t="n">
-        <v/>
+      <c r="E30" s="5" t="n">
+        <v>2.27</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
@@ -1883,11 +1891,11 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v/>
+        <v>-1.85</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
@@ -1929,11 +1937,11 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v/>
+        <v>-2.89</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
@@ -1974,12 +1982,12 @@
           <t>1454.6</t>
         </is>
       </c>
-      <c r="E33" s="3" t="n">
-        <v/>
+      <c r="E33" s="5" t="n">
+        <v>2.88</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
@@ -2020,12 +2028,12 @@
           <t>5166.0</t>
         </is>
       </c>
-      <c r="E34" s="3" t="n">
-        <v/>
+      <c r="E34" s="5" t="n">
+        <v>1.32</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
@@ -2067,11 +2075,11 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v/>
+        <v>-1.16</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
@@ -2112,12 +2120,12 @@
           <t>171.1</t>
         </is>
       </c>
-      <c r="E36" s="3" t="n">
-        <v/>
+      <c r="E36" s="5" t="n">
+        <v>3.74</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
@@ -2158,12 +2166,12 @@
           <t>1047.5</t>
         </is>
       </c>
-      <c r="E37" s="3" t="n">
-        <v/>
+      <c r="E37" s="5" t="n">
+        <v>1.19</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
@@ -2205,11 +2213,11 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v/>
+        <v>-0.62</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
@@ -2251,11 +2259,11 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v/>
+        <v>-1.07</v>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
@@ -2297,11 +2305,11 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v/>
+        <v>-0.89</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
@@ -2342,12 +2350,12 @@
           <t>2050.0</t>
         </is>
       </c>
-      <c r="E41" s="3" t="n">
-        <v/>
+      <c r="E41" s="5" t="n">
+        <v>3.3</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
@@ -2389,11 +2397,11 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v/>
+        <v>-1.31</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
@@ -2435,11 +2443,11 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v/>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
@@ -2480,12 +2488,12 @@
           <t>504.0</t>
         </is>
       </c>
-      <c r="E44" s="3" t="n">
-        <v/>
+      <c r="E44" s="5" t="n">
+        <v>1.13</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
@@ -2526,12 +2534,12 @@
           <t>679.8</t>
         </is>
       </c>
-      <c r="E45" s="3" t="n">
-        <v/>
+      <c r="E45" s="5" t="n">
+        <v>1.65</v>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
@@ -2573,11 +2581,11 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v/>
+        <v>-2.61</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
@@ -2618,12 +2626,12 @@
           <t>314.3</t>
         </is>
       </c>
-      <c r="E47" s="3" t="n">
-        <v/>
+      <c r="E47" s="5" t="n">
+        <v>2.13</v>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
@@ -2664,12 +2672,12 @@
           <t>7490.0</t>
         </is>
       </c>
-      <c r="E48" s="3" t="n">
-        <v/>
+      <c r="E48" s="5" t="n">
+        <v>1.72</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
@@ -2710,12 +2718,12 @@
           <t>1637.0</t>
         </is>
       </c>
-      <c r="E49" s="3" t="n">
-        <v/>
+      <c r="E49" s="5" t="n">
+        <v>4.36</v>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
@@ -2756,12 +2764,12 @@
           <t>882.4</t>
         </is>
       </c>
-      <c r="E50" s="3" t="n">
-        <v/>
+      <c r="E50" s="5" t="n">
+        <v>1.85</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
@@ -2803,11 +2811,11 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v/>
+        <v>-0.3</v>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
@@ -2849,11 +2857,11 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v/>
+        <v>-1.01</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
@@ -2895,11 +2903,11 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v/>
+        <v>-0.43</v>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
@@ -2940,12 +2948,12 @@
           <t>11910.0</t>
         </is>
       </c>
-      <c r="E54" s="3" t="n">
-        <v/>
+      <c r="E54" s="5" t="n">
+        <v>1.85</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
@@ -2986,12 +2994,12 @@
           <t>1656.0</t>
         </is>
       </c>
-      <c r="E55" s="3" t="n">
-        <v/>
+      <c r="E55" s="5" t="n">
+        <v>3.57</v>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
@@ -3033,11 +3041,11 @@
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v/>
+        <v>-1.32</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
@@ -3079,11 +3087,11 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v/>
+        <v>-0.79</v>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
@@ -3125,11 +3133,11 @@
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v/>
+        <v>-0.02</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
@@ -3171,11 +3179,11 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v/>
+        <v>-2.14</v>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
@@ -3216,12 +3224,12 @@
           <t>2002.0</t>
         </is>
       </c>
-      <c r="E60" s="3" t="n">
-        <v/>
+      <c r="E60" s="5" t="n">
+        <v>0.95</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
@@ -3263,11 +3271,11 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v/>
+        <v>-1.29</v>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
@@ -3282,6 +3290,2766 @@
         <v/>
       </c>
       <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>1717.0</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>349.55</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>1086.2</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>20108.0</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>12130.0</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>50000.0</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14850.0</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>1148.7</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>3371.0</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>1192.9</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>691.05</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>1276.0</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>1161.3</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>3400.0</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>2205.0</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>1454.0</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>1915.0</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>1717.7</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>1875.0</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>782.0</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>813.05</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>483.15</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>1687.7</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>380.35</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>1868.0</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>456.2</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>3282.0</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>177.5</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>5234.0</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>1628.0</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>737.9</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>1060.0</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>2427.4</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>1900.0</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>2104.9</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>1496.5</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>175.64</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>2021.0</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>2021.0</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>3282.0</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>1057.0</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>1857.4</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>1060.0</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>691.05</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>170.68</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>1148.7</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>1276.0</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>1175.0</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>813.05</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>114.23</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>1984.8</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>5102.4</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>4341.3</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>380.35</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>12130.0</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>1687.7</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>8898.5</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>5066.0</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3360,16 +6128,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -3400,16 +6168,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -3440,16 +6208,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -3480,16 +6248,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">

--- a/Analysis/exports/backtest_results.xlsx
+++ b/Analysis/exports/backtest_results.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J121"/>
+  <dimension ref="A1:J224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v/>
+        <v>-1.75</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v/>
+        <v>-1.6</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v/>
+        <v>-5.16</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v/>
+        <v>-4.08</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -657,15 +657,15 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v/>
+        <v>-1.93</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I4" s="3" t="n">
-        <v/>
+      <c r="I4" s="5" t="n">
+        <v>0.52</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v/>
+        <v>-1.84</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v/>
+        <v>-2.89</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v/>
+        <v>-4.19</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v/>
+        <v>-2.76</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -794,8 +794,8 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G7" s="3" t="n">
-        <v/>
+      <c r="G7" s="5" t="n">
+        <v>0.52</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v/>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -840,16 +840,16 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="G8" s="3" t="n">
-        <v/>
+      <c r="G8" s="5" t="n">
+        <v>0.98</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I8" s="3" t="n">
-        <v/>
+      <c r="I8" s="5" t="n">
+        <v>5.12</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -886,8 +886,8 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G9" s="3" t="n">
-        <v/>
+      <c r="G9" s="5" t="n">
+        <v>4.32</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v/>
+        <v>-2</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v/>
+        <v>-1.16</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v/>
+        <v>-2.37</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v/>
+        <v>-2.16</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v/>
+        <v>-0.74</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v/>
+        <v>-1.09</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v/>
+        <v>-2.68</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v/>
+        <v>-0.26</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v/>
+        <v>-1.08</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v/>
+        <v>-1.71</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v/>
+        <v>-2.74</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v/>
+        <v>-2.43</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v/>
+        <v>-2.07</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v/>
+        <v>-3.09</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v/>
+        <v>-5.96</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v/>
+        <v>-3.84</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v/>
+        <v>-5.08</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v/>
+        <v>-2.09</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v/>
+        <v>-3</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v/>
+        <v>-8.73</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v/>
+        <v>-7.27</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1392,16 +1392,16 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G20" s="3" t="n">
-        <v/>
+      <c r="G20" s="5" t="n">
+        <v>1.17</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I20" s="3" t="n">
-        <v/>
+      <c r="I20" s="5" t="n">
+        <v>5.06</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1438,16 +1438,16 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G21" s="3" t="n">
-        <v/>
+      <c r="G21" s="5" t="n">
+        <v>0.78</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I21" s="3" t="n">
-        <v/>
+      <c r="I21" s="5" t="n">
+        <v>1.04</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v/>
+        <v>-2.22</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v/>
+        <v>-1.8</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v/>
+        <v>-3.11</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v/>
+        <v>-3.12</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v/>
+        <v>-2.64</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v/>
+        <v>-1.73</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v/>
+        <v>-1.04</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v/>
+        <v>-2.25</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v/>
+        <v>-1.69</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v/>
+        <v>-1.56</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -1714,8 +1714,8 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="G27" s="3" t="n">
-        <v/>
+      <c r="G27" s="5" t="n">
+        <v>1.17</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v/>
+        <v>-1.72</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -1760,8 +1760,8 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G28" s="3" t="n">
-        <v/>
+      <c r="G28" s="5" t="n">
+        <v>0.36</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v/>
+        <v>-2.31</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v/>
+        <v>-1.67</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v/>
+        <v>-0.1</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -1853,15 +1853,15 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v/>
+        <v>-1.61</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I30" s="3" t="n">
-        <v/>
+      <c r="I30" s="5" t="n">
+        <v>1.46</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v/>
+        <v>-1.92</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v/>
+        <v>-2.89</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v/>
+        <v>-2.06</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v/>
+        <v>-3.45</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v/>
+        <v>-2.03</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v/>
+        <v>-3.03</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v/>
+        <v>-2.83</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v/>
+        <v>-3.66</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v/>
+        <v>-0.04</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v/>
+        <v>-1.75</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -2128,16 +2128,16 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G36" s="3" t="n">
-        <v/>
+      <c r="G36" s="5" t="n">
+        <v>1.4</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I36" s="3" t="n">
-        <v/>
+      <c r="I36" s="5" t="n">
+        <v>1.64</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v/>
+        <v>-2.54</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v/>
+        <v>-3</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v/>
+        <v>-1.58</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v/>
+        <v>-1.55</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v/>
+        <v>-2.41</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v/>
+        <v>-2.37</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v/>
+        <v>-4.63</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v/>
+        <v>-3.42</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v/>
+        <v>-0.29</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v/>
+        <v>-4.01</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v/>
+        <v>-4.31</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v/>
+        <v>-5.32</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v/>
+        <v>-4.48</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v/>
+        <v>-3.85</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v/>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v/>
+        <v>-1.58</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -2543,15 +2543,15 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v/>
+        <v>-0.92</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I45" s="3" t="n">
-        <v/>
+      <c r="I45" s="5" t="n">
+        <v>0.31</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v/>
+        <v>-2.8</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v/>
+        <v>-2.41</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v/>
+        <v>-0.48</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v/>
+        <v>-0.1</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v/>
+        <v>-0.82</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v/>
+        <v>-1.32</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -2726,16 +2726,16 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G49" s="3" t="n">
-        <v/>
+      <c r="G49" s="5" t="n">
+        <v>0.18</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I49" s="3" t="n">
-        <v/>
+      <c r="I49" s="5" t="n">
+        <v>0.47</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v/>
+        <v>-0.41</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v/>
+        <v>-0.31</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v/>
+        <v>-1.99</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v/>
+        <v>-1.28</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -2864,16 +2864,16 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="G52" s="3" t="n">
-        <v/>
+      <c r="G52" s="5" t="n">
+        <v>1.39</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I52" s="3" t="n">
-        <v/>
+      <c r="I52" s="5" t="n">
+        <v>1.39</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -2910,16 +2910,16 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="G53" s="3" t="n">
-        <v/>
+      <c r="G53" s="5" t="n">
+        <v>1.94</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I53" s="3" t="n">
-        <v/>
+      <c r="I53" s="5" t="n">
+        <v>8.470000000000001</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -2956,16 +2956,16 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G54" s="3" t="n">
-        <v/>
+      <c r="G54" s="5" t="n">
+        <v>1.85</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I54" s="3" t="n">
-        <v/>
+      <c r="I54" s="5" t="n">
+        <v>0.08</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -3002,8 +3002,8 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G55" s="3" t="n">
-        <v/>
+      <c r="G55" s="5" t="n">
+        <v>0.46</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v/>
+        <v>-2.68</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="I56" s="3" t="n">
-        <v/>
+        <v>-2.54</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v/>
+        <v>-1.09</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v/>
+        <v>-2.68</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v/>
+        <v>-1.6</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v/>
+        <v>-2.02</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v/>
+        <v>-2.92</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I59" s="3" t="n">
-        <v/>
+        <v>-4.45</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v/>
+        <v>-0.6</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v/>
+        <v>-1.6</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v/>
+        <v>-1.84</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="I61" s="3" t="n">
-        <v/>
+        <v>-2.89</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v/>
+        <v>-1.96</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v/>
+        <v>-4.64</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v/>
+        <v>-3.16</v>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v/>
+        <v>-4.39</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v/>
+        <v>-0.64</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v/>
+        <v>-1.31</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3455,15 +3455,15 @@
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v/>
+        <v>-0.24</v>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G65" s="3" t="n">
-        <v/>
+      <c r="G65" s="5" t="n">
+        <v>6.92</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
@@ -3500,8 +3500,8 @@
           <t>12130.0</t>
         </is>
       </c>
-      <c r="E66" s="3" t="n">
-        <v/>
+      <c r="E66" s="5" t="n">
+        <v>1.9</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v/>
+        <v>-1.73</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v/>
+        <v>-2.9</v>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v/>
+        <v>-6</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v/>
+        <v>-2.62</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v/>
+        <v>-2.73</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3638,8 +3638,8 @@
           <t>1148.7</t>
         </is>
       </c>
-      <c r="E69" s="3" t="n">
-        <v/>
+      <c r="E69" s="5" t="n">
+        <v>0.29</v>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v/>
+        <v>-0.28</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v/>
+        <v>-1.96</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v/>
+        <v>-1.81</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v/>
+        <v>-2.76</v>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v/>
+        <v>-4.02</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v/>
+        <v>-2.3</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v/>
+        <v>-1.36</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v/>
+        <v>-2.85</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v/>
+        <v>-4.55</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v/>
+        <v>-0.13</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v/>
+        <v>-0.55</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3914,8 +3914,8 @@
           <t>1161.3</t>
         </is>
       </c>
-      <c r="E75" s="3" t="n">
-        <v/>
+      <c r="E75" s="5" t="n">
+        <v>0.5600000000000001</v>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v/>
+        <v>-1.58</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v/>
+        <v>-2.85</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v/>
+        <v>-6.76</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v/>
+        <v>-1.14</v>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v/>
+        <v>-2.4</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v/>
+        <v>-1.1</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v/>
+        <v>-1.65</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v/>
+        <v>-2.79</v>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v/>
+        <v>-2.43</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
@@ -4144,8 +4144,8 @@
           <t>1717.7</t>
         </is>
       </c>
-      <c r="E80" s="3" t="n">
-        <v/>
+      <c r="E80" s="5" t="n">
+        <v>0.46</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v/>
+        <v>-4.59</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v/>
+        <v>-2.44</v>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v/>
+        <v>-0.27</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v/>
+        <v>-3.84</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v/>
+        <v>-4.42</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v/>
+        <v>-0.44</v>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v/>
+        <v>-1.61</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
@@ -4328,16 +4328,16 @@
           <t>483.15</t>
         </is>
       </c>
-      <c r="E84" s="3" t="n">
-        <v/>
+      <c r="E84" s="5" t="n">
+        <v>1.42</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G84" s="3" t="n">
-        <v/>
+      <c r="G84" s="5" t="n">
+        <v>1.42</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v/>
+        <v>-2.62</v>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v/>
+        <v>-2.93</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
@@ -4420,16 +4420,16 @@
           <t>380.35</t>
         </is>
       </c>
-      <c r="E86" s="3" t="n">
-        <v/>
+      <c r="E86" s="5" t="n">
+        <v>0.04</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G86" s="3" t="n">
-        <v/>
+      <c r="G86" s="5" t="n">
+        <v>7.3</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4466,16 +4466,16 @@
           <t>1868.0</t>
         </is>
       </c>
-      <c r="E87" s="3" t="n">
-        <v/>
+      <c r="E87" s="5" t="n">
+        <v>0.68</v>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G87" s="3" t="n">
-        <v/>
+      <c r="G87" s="5" t="n">
+        <v>1.82</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
@@ -4512,16 +4512,16 @@
           <t>456.2</t>
         </is>
       </c>
-      <c r="E88" s="3" t="n">
-        <v/>
+      <c r="E88" s="5" t="n">
+        <v>1.01</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G88" s="3" t="n">
-        <v/>
+      <c r="G88" s="5" t="n">
+        <v>1.79</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v/>
+        <v>-0.7</v>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v/>
+        <v>-4.02</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v/>
+        <v>-2.71</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v/>
+        <v>-1.31</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v/>
+        <v>-2.85</v>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v/>
+        <v>-4.55</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v/>
+        <v>-3.48</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v/>
+        <v>-4.85</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4742,8 +4742,8 @@
           <t>1628.0</t>
         </is>
       </c>
-      <c r="E93" s="3" t="n">
-        <v/>
+      <c r="E93" s="5" t="n">
+        <v>0.61</v>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v/>
+        <v>-1.84</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v/>
+        <v>-2.7</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v/>
+        <v>-0.8</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v/>
+        <v>-2.41</v>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v/>
+        <v>-3.45</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
@@ -4880,16 +4880,16 @@
           <t>2427.4</t>
         </is>
       </c>
-      <c r="E96" s="3" t="n">
-        <v/>
+      <c r="E96" s="5" t="n">
+        <v>3.22</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G96" s="3" t="n">
-        <v/>
+      <c r="G96" s="5" t="n">
+        <v>1.8</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4927,15 +4927,15 @@
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v/>
+        <v>-0.39</v>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G97" s="3" t="n">
-        <v/>
+      <c r="G97" s="5" t="n">
+        <v>3.16</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v/>
+        <v>-2.5</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v/>
+        <v>-5.89</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v/>
+        <v>-3.9</v>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v/>
+        <v>-5.38</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v/>
+        <v>-2.91</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v/>
+        <v>-3.58</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v/>
+        <v>-2.42</v>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v/>
+        <v>-1.43</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v/>
+        <v>-2.42</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v/>
+        <v>-1.43</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v/>
+        <v>-0.7</v>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v/>
+        <v>-4.02</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v/>
+        <v>-0.29</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v/>
+        <v>-0.76</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v/>
+        <v>-2.3</v>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v/>
+        <v>-0.44</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v/>
+        <v>-2.41</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="G106" s="3" t="n">
-        <v/>
+        <v>-3.45</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v/>
+        <v>-2.3</v>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="G107" s="3" t="n">
-        <v/>
+        <v>-1.36</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v/>
+        <v>-2.98</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         </is>
       </c>
       <c r="G108" s="3" t="n">
-        <v/>
+        <v>-5.09</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -5478,8 +5478,8 @@
           <t>1148.7</t>
         </is>
       </c>
-      <c r="E109" s="3" t="n">
-        <v/>
+      <c r="E109" s="5" t="n">
+        <v>0.29</v>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="G109" s="3" t="n">
-        <v/>
+        <v>-0.28</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="E110" s="3" t="n">
-        <v/>
+        <v>-0.13</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="G110" s="3" t="n">
-        <v/>
+        <v>-0.55</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v/>
+        <v>-0.8</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="G111" s="3" t="n">
-        <v/>
+        <v>-1.7</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v/>
+        <v>-0.44</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="G112" s="3" t="n">
-        <v/>
+        <v>-1.61</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5662,16 +5662,16 @@
           <t>114.23</t>
         </is>
       </c>
-      <c r="E113" s="3" t="n">
-        <v/>
+      <c r="E113" s="5" t="n">
+        <v>0.87</v>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G113" s="3" t="n">
-        <v/>
+      <c r="G113" s="5" t="n">
+        <v>1.83</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         </is>
       </c>
       <c r="E114" s="3" t="n">
-        <v/>
+        <v>-2.81</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="G114" s="3" t="n">
-        <v/>
+        <v>-3.47</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="E115" s="3" t="n">
-        <v/>
+        <v>-1.03</v>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="G115" s="3" t="n">
-        <v/>
+        <v>-1.48</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v/>
+        <v>-3.19</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="G116" s="3" t="n">
-        <v/>
+        <v>-3.25</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5846,16 +5846,16 @@
           <t>380.35</t>
         </is>
       </c>
-      <c r="E117" s="3" t="n">
-        <v/>
+      <c r="E117" s="5" t="n">
+        <v>0.04</v>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G117" s="3" t="n">
-        <v/>
+      <c r="G117" s="5" t="n">
+        <v>7.3</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
@@ -5892,8 +5892,8 @@
           <t>12130.0</t>
         </is>
       </c>
-      <c r="E118" s="3" t="n">
-        <v/>
+      <c r="E118" s="5" t="n">
+        <v>1.9</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="G118" s="3" t="n">
-        <v/>
+        <v>-1.73</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v/>
+        <v>-2.62</v>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         </is>
       </c>
       <c r="G119" s="3" t="n">
-        <v/>
+        <v>-2.93</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v/>
+        <v>-1.61</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="G120" s="3" t="n">
-        <v/>
+        <v>-2.32</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="E121" s="3" t="n">
-        <v/>
+        <v>-1.98</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="G121" s="3" t="n">
-        <v/>
+        <v>-3.17</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
@@ -6053,6 +6053,4126 @@
         <is>
           <t>—</t>
         </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I122" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>289.5</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H123" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I123" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J123" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>489.0</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I124" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>1143.0</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H125" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I125" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J125" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>21500.0</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I126" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>1870.0</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="F127" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H127" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I127" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J127" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>431.8</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I128" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>334.2</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H129" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J129" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>895.0</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I130" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>1430.0</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="F131" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H131" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I131" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J131" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>189.0</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I132" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>888.75</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H133" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I133" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J133" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>3310.0</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I134" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J134" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>408.1</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F135" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H135" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J135" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>1902.0</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I136" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>1234.0</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="F137" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G137" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H137" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I137" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J137" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>11920.0</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I138" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>681.65</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F139" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H139" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I139" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J139" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>9250.0</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I140" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J140" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>4905.5</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="F141" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H141" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I141" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J141" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>9100.0</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G142" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I142" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J142" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>488.3</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F143" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H143" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I143" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J143" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>11919.0</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I144" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J144" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>1836.0</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F145" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H145" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I145" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J145" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>173.4</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I146" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>1972.8</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F147" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H147" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I147" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J147" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>1596.9</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I148" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>681.9</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F149" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G149" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H149" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I149" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J149" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>1653.1</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I150" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>3322.0</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H151" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I151" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J151" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>431.1</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I152" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>12058.0</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F153" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H153" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I153" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J153" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>1166.0</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I154" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>1584.0</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F155" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H155" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I155" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J155" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>86.71</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I156" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>891.0</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F157" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G157" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H157" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I157" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J157" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>4857.0</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I158" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>598.8</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F159" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G159" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H159" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I159" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J159" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>1394.6</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I160" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>Probable Upside</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>187.22</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F161" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H161" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I161" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J161" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>2368.8</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G162" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I162" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>1394.0</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F163" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G163" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H163" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I163" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J163" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>2001.5</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I164" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>289.5</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="F165" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H165" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I165" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J165" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>11165.0</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F166" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G166" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H166" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I166" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>1072.0</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F167" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H167" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I167" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J167" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>8692.0</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G168" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I168" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>1638.3</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="F169" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G169" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H169" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I169" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J169" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>1394.7</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G170" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I170" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>1143.0</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="F171" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G171" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H171" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I171" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J171" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>1308.0</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G172" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I172" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>2474.0</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F173" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G173" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H173" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I173" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J173" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>316.9</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G174" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I174" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>1416.0</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="F175" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G175" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H175" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I175" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J175" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>464.35</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G176" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H176" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I176" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>4362.0</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F177" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G177" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H177" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I177" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J177" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>286.0</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G178" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I178" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>7410.0</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F179" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G179" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H179" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I179" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J179" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>1234.0</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="F180" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G180" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H180" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I180" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>747.4</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F181" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G181" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H181" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I181" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J181" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>36300.0</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F182" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G182" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H182" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I182" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="inlineStr">
+        <is>
+          <t>1394.6</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F183" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G183" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H183" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I183" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J183" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>601.0</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G184" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H184" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I184" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
+          <t>2475.0</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F185" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G185" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H185" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I185" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J185" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>1410.5</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F186" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G186" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H186" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I186" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J186" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr">
+        <is>
+          <t>84.7</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F187" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G187" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H187" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I187" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J187" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>8650.0</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F188" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G188" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H188" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I188" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J188" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr">
+        <is>
+          <t>1385.0</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F189" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G189" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H189" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I189" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J189" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>1166.0</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F190" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G190" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H190" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I190" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J190" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="D191" s="4" t="inlineStr">
+        <is>
+          <t>2938.0</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F191" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G191" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H191" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I191" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J191" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>7474.0</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F192" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G192" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H192" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I192" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J192" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t>457.9</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F193" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G193" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H193" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I193" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J193" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>3409.8</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F194" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G194" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H194" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I194" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J194" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr">
+        <is>
+          <t>1301.3</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F195" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G195" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H195" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I195" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J195" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>562.3</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F196" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G196" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H196" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I196" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J196" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>374.1</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F197" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G197" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H197" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I197" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J197" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>339.7</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F198" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G198" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H198" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I198" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J198" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t>1982.0</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F199" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G199" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H199" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I199" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J199" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>288.1</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F200" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G200" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H200" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I200" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J200" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>Support Entry</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr">
+        <is>
+          <t>5020.0</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F201" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G201" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H201" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I201" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J201" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>1992.1</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="F202" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G202" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H202" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I202" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J202" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="D203" s="4" t="inlineStr">
+        <is>
+          <t>5027.0</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="F203" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G203" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H203" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I203" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J203" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>4559.0</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="F204" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G204" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H204" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I204" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J204" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="D205" s="4" t="inlineStr">
+        <is>
+          <t>1849.3</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="F205" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G205" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H205" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I205" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J205" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>1638.3</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="F206" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G206" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H206" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I206" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J206" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="D207" s="4" t="inlineStr">
+        <is>
+          <t>116.32</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F207" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G207" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H207" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I207" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J207" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G208" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H208" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I208" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J208" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="D209" s="4" t="inlineStr">
+        <is>
+          <t>7432.0</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="F209" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G209" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H209" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I209" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J209" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>1269.0</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="F210" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G210" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H210" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I210" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J210" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="D211" s="4" t="inlineStr">
+        <is>
+          <t>1145.5</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="F211" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G211" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H211" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I211" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J211" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>189.0</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="F212" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G212" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H212" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I212" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J212" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="D213" s="4" t="inlineStr">
+        <is>
+          <t>1330.0</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="F213" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G213" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H213" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I213" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J213" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>5020.0</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F214" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G214" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H214" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I214" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J214" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="D215" s="4" t="inlineStr">
+        <is>
+          <t>1970.0</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F215" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G215" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H215" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I215" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J215" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>4494.0</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F216" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G216" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H216" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I216" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J216" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="D217" s="4" t="inlineStr">
+        <is>
+          <t>1839.0</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F217" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G217" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H217" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I217" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J217" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F218" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G218" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H218" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I218" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J218" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="D219" s="4" t="inlineStr">
+        <is>
+          <t>7410.0</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F219" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G219" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H219" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I219" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J219" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>3977.0</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F220" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G220" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H220" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I220" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J220" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="D221" s="4" t="inlineStr">
+        <is>
+          <t>1249.7</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F221" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G221" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H221" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I221" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J221" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>1166.0</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F222" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G222" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H222" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I222" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J222" s="2" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="D223" s="4" t="inlineStr">
+        <is>
+          <t>322.75</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F223" s="4" t="n">
+        <v/>
+      </c>
+      <c r="G223" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H223" s="4" t="n">
+        <v/>
+      </c>
+      <c r="I223" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J223" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation Breakout</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>1319.8</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F224" s="2" t="n">
+        <v/>
+      </c>
+      <c r="G224" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H224" s="2" t="n">
+        <v/>
+      </c>
+      <c r="I224" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J224" s="2" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -6128,36 +10248,36 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>120</v>
+        <v>223</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.61%</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.60%</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.63%</t>
         </is>
       </c>
     </row>
@@ -6168,36 +10288,36 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-0.90%</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.99%</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.78%</t>
         </is>
       </c>
     </row>
@@ -6208,36 +10328,36 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.50%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-2.03%</t>
         </is>
       </c>
     </row>
@@ -6248,36 +10368,36 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.30%</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.08%</t>
         </is>
       </c>
     </row>
